--- a/reports/visit_details/visit_details_ntombizodwa-zodwa-dubazana.xlsx
+++ b/reports/visit_details/visit_details_ntombizodwa-zodwa-dubazana.xlsx
@@ -419,11 +419,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D325"/>
+  <dimension ref="A1:D568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
@@ -7578,6 +7578,5352 @@
         </is>
       </c>
     </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>0404205722089</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Ntobeko Ntshele</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>9408135192082</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Sibusiso Mjoli</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>0511032100188</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Boitumelo Mabitsela</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>0502105263086</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Nhlaka Maseko</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>0404300744087</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Mpfumelelo Mchavi</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>6109170207081</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Thabo Motaung</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>7007300567086</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Thabiso Motaung</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>7411115259089</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Siphesihle Molapo</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>7004075594080</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Lethuxolo Xolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>0506036879082</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Katlego Tshwene</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>0204285767082</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Mamello Thene</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>0509125678086</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Rethabile Thene</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>9912167989088</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Kgomotso Thene</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>0312240307081</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Priscilla Sotyhamty</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>9707165286088</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Thabani Mthembu</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>0210267588082</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Owami Sibanyoni</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>9707240956083</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Kagiso Malebati</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>0511050591086</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Eunice Maswanganyi</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>8101085942082</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Samkelo Vilakazi</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>0602245602084</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Khetha Cele</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>5802030786085</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Nobuhle Mbele</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>9906035275089</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Mtando Rasmeni</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>6904250969083</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Nozuko Moloi</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>8002190503084</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Zoleka Klaas</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>0306306243081</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Evuya Gobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>8307100390088</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Dephney Matshinye</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>0306200940089</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Bongisisa Ntetha</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>0309245624080</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Xolane Mbuli</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>9610032060782</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Mamahlogonolo Mohlala</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>6411150462086</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Dumazile Mncunu</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>5603060774086</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Kelebogile Tsonyane</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>8101010372082</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Duduzile Duma</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>8402200601096</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Nokufika Manana</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>8204075549089</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Bataung Lefatle</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>0012314630083</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Tinyiko Mathebula</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>9305177600084</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Thabiso Zungu</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>0503106074084</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Celani Mthembu</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>0505010521084</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Eberechuk Richard</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>0512260175082</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Sinazo Skhosana</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>0606260089085</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Gugu Sithebe</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>0511300964083</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Esihle Sigagayi</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>0310170107083</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Mphoh Mvubu</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>6811285271080</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Joyce Gumede</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>0404205722089</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Nomusa Thusi</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>0508101139089</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Lindo Buthelezi</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>8509156515084</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Sithembiso Xolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>8005105857081</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Mhlengikazi Mbense</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>7709270848087</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Jackson Mlambo</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>9906224472083</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Amogelang Kanedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>0006305475086</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Innocent Mbuli</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>9510248753088</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Thabang Malinga</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>0307315299080</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Hope Gqalangile</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>0505220545089</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Vuthi Baloyi</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>0509155457088</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Bongane Gqalangile</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>9702249620885</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Hope Mashamba</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>0306100776088</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Buhle Gqalangile</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>7706020917089</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Khumo Mantsho</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>9709276906983</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Michael Msimanga</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>6412125948084</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Shaka Machapa</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>6906143462081</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Happy Dodovu</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>8101162880680</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Ntswaki Dodovu</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>6412125948084</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Calvin Molata</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>9804285373082</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Luvuyo Dodovu</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>9912133670882</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Kamogelo Pule</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>8304290312089</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Omphemetse Prince</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>9704067810183</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Boikanyo Matlala</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>6312075126089</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Omolemo Segakwena</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>8403120565089</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Lonwabo Mzuko</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>9-Oct</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>8503075042087</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Gaborona Madi</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>0501280898088</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Nonhlanhla Gqalangile</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>0502131110087</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Mpho Selepe</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>9710290464085</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Mbhali Msibi</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>0501210338080</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Thandiswa Tsangani</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>0208190907088</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Noluthando Dyumba</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>0605235269087</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Tlotliso Sihlali</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>9795295278084</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Katleho Mabine</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>9902050443082</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Unathi Dyodyo</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>0201031428083</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Seipati Motloung</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>9701149779086</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Thabiso Moloi</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>0307070960082</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Londeka Gabela</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>0602285474089</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Quincy Williams</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>0604231111088</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Alexandre Limao</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>0010010090081</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Thubelihle Khumalo</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>0311221036081</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Akhona Mtshali</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>0106227597082</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Tendani Ndlovu</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>9810120683089</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Nombuso Mpumulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>8512030686087</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>John Mayidi</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>9712030376087</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Lithemba Mzayifani</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>650304567392</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Karabelo Ngobeni</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>8703125676087</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Sibusiso Hlatshwayo</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>8606120676084</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Nandipha Letsoko</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>7704170457089</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Thandi Polo</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>7110290478080</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Princess Hlongwane</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>5712260234085</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Palesa Ntuli</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>0411195128086</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Thenji Shabalala</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>0508101139089</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Siya Kheswa</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>6002275606085</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Mbulelo Ngemntu</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>0208235787082</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Bokamoso Phetwane</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>7609060947083</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Kgakgamatso Moleta</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>8504275979089</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Zilungisele Dzanibe</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>6706021088089</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Simphiwe Mzitho</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>7602215401080</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Tshepiso Gauta</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>8505050255082</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Buyisile Mazibuko</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>7902120622089</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Motsatsi Ramodike</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>8003036957088</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Matome Malemela</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>6309120216089</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Zukiswa Magqaza</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>8310130617082</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Fundiswa Gwaxula</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>7506207035085</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Dumisani Mathaba</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>7305210290082</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Nompumelelo Magoso</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>7902240688085</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Thandiwe Mukasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>7809295542085</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Xolani Fulmeni</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>6403220287080</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Moloko Makgoka</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>8803315491083</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Prince Mahlangu</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>7403280321083</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Gcinephi Thabede</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>8108260396083</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Silindile Ngcongo</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>0507040861084</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Kelebogile Mokoena</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>0508145579084</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Rise Lusibi</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>8201248182085</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Kgaugelo Mekoa</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>9812230365086</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Luyanda Davashe</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>8702130456087</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Pontsho Zulu</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>0605085461081</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Mbuso Zikhali</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>8712130775086</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Pakiso Gumba</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>0605085461081</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Kwanda Ziqubu</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>0211265288087</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Lebo Motaung</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>8901120724083</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Tsepang Modise</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>9310218475086</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Tumelo Mashiane</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>9803125432087</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Tumelo Mashiane</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>8703120345085</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Phumzile Makhanya</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>9304264534086</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Mpho Mokale</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>8404244534074</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Katlego Mbasa</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>8703135463086</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Ayanda Khonyane</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>7304036463083</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Nqobile Mpofu</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>8910020626063</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Tshepiso Lebati</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>891205576082</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Jeffery Hlongwane</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>8903230567072</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Lonwabo Mzuko</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>0020323067087</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Monde Nonyusa</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>9801015969786</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Blessing Mohlala</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>0608293040183</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Nothando Mathebula</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>0411171180085</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Sne Tembe</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>0209115676082</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Mosa Petlane</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>9911052185983</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Mosa Mathye</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>0005121138082</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Nolitha Mabuza</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>9606131139082</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Thobile Jali</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>0411171180085</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Thandi Mokoena</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>9004125286088</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Sipho Radebe</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>9703245618982</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Sipho Dlamini</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>9910125175086</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Alex Moema</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>9912287879088</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Tebogo Sepane</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>930326787081</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Khaya Ndiba</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>970926792185</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Nhlakanipo Ncube</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>960817821088</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Sio Hani</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>0511211032087</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Senamile Khumalo</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>0209191132086</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Masindi Mbhele</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>9910220178086</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Rethabile Mosola</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>8902297959083</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Katlego Phiri</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>0605016188084</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Karabo Mamabolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>9001013788086</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Ribone Seloane</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>00101908100084</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Tintswalo Mabaso</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>0602215759086</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Ntandokazi Duma</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>9705040206083</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Thokozile Gambu</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>9910267978088</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Mpho Yende</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>9710010831084</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Zakhona Chonco</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>9805191159084</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Zinhle Buthelezi</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>0001041021084</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Precious Maswanganye</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>9507155386088</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Sihle Langa</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>9709070420080</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Buhle Nonjola</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>0605016188084</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Vuyolwethu Ngubane</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>0409175243081</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Tumi Mofolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>0401175364084</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Lisakhanya Mgibantaka</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>0108135794080</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Esethu Dywili</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>0002171112084</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Lucky Mkhinanazi</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>0010225080080</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Khutso Gaope</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>9601230592080</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Kagiso Monametsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>10-Oct</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>9512288039084</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Katlego Nkwe</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>7606295681081</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Nkosinathi Khwela</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>7802075771081</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Siyabulela Mcimbi</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>8602055831080</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Mncedisi Nyathi</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>6202080634088</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Sandrah Mohlala</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>8201090740081</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Mokgadi Mokoto</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>7903215616083</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Nombulelo Xuma</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>8403120365087</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Nomeva Msumbulu</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>0605016188084</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Sipho Lila</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>9903250626087</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Xolani Nkabinde</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>0040621042086</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Thato Radebe</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>0040315682086</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Atlegang Ramathibela</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>841110</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Thenjiwe Mashexa</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>8507050578083</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Omaatla Pebe</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>8408290841086</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Katlego Khumalo</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>0409175243081</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Khoho Lesesa</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>0405045207082</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Zimbili Khumalo</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>7907040773086</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Lindiwe Zulu</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>7608190745086</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Amanda Maneli</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>7204255865082</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Luthando Gumede</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>7408045599089</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Lawrence Molongwana</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>6510110236082</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Thoko Mabaso</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>7311270741089</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Reinette Matsimela</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>7909230483088</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Nkosazana Maham</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>7503076016084</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Alfred Mzolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>82060740520087</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Mpumelelo Zulu</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>7310115780088</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Boitumelo Nkosi</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>0406270218083</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Nomthandazo Mtungwa</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>7202280934089</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Nathi Nkosi</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>8705160354087</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Nothando Simelane</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>8405315502081</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Kegomoditswe Motlhoiwa</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>8009180662085</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Neo Maswanganye</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>9812044508087</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Ntombi Ncongwane</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>7209280624087</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Lerato Nkosi</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>5806067165089</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Vuyo Gambu</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>9807073576075</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Ayanda Mazibuko</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>7510102777084</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Keneiloe Madigoe</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>8912046712073</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Njabulo Mthambo</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>9806126476076</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Thabang Mpungose</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>0601214600283</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Khensane Ngobeni</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>9406279874081</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Tebogo Seloke</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>8912210632086</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Sphisethu Sibiya</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>9701264550076</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Thato Mazibuko</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>9807126576087</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Sabelo Ndlovu</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>9903163544081</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Cwaka Tansi</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>0308220314089</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Khanyi Motha</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>0505245090087</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Chaneva Milandou</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>8111025611085</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Simphiwe Gogi</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>7109175811084</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Bongani Nkuzni</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>5511110755080</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Nunutsha Mashele</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>7808160695085</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Mokgwale Sejaphala</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>8004300217084</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Mmadinji Nkoana</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>0509290257088</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Chloe Naicker</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>6708065629083</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Barataung Kgwele</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>6911260624087</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Phumele Hadebe</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>0602142533082</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Zama Buthelezi</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>9408171139082</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Mpilonhle Hlophe</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>0507226579082</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Luvuyo Kose</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>9904237568085</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Malesela Lamola</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>980516321083</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Keabetswe Mahlangu</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>7012030374083</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Nobuhle Khuzwayo</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>8503280750080</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Zamokuhle Zwai</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>0208121130087</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Zonhle Mangope</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>0205020350883</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Julia Fernando</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>0018120802080</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Kagiso Zulu</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>0212310820011</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Katlego Nkosi</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>7009260865088</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Nolwazi Gumbi</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>0504181266082</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Asanda Zwane</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>9509284060183</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Puseletso Netshavhela</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Ntombizodwa Zodwa Dubazana</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>0002184676082</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Refiloe Netshavhela</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
